--- a/test-data/テスト用置換データ.xlsx
+++ b/test-data/テスト用置換データ.xlsx
@@ -1,40 +1,748 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <workbookPr showInkAnnotation="0" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ImaiK\Desktop\Wordファイル一括複製ツール\お試し用ファイル\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{475889E6-EB0B-482B-B249-2A6AD480A011}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="390" yWindow="480" windowWidth="19140" windowHeight="14820" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="申請者一覧表" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="申請者一覧表" sheetId="5" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">申請者一覧表!$A$1:$N$22</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">申請者一覧表!$1:$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="89">
+  <si>
+    <t>学校名</t>
+    <rPh sb="0" eb="2">
+      <t>ガッコウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>メイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学年</t>
+    <rPh sb="0" eb="2">
+      <t>ガクネン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>預金種別
+普通：１
+当座：２</t>
+    <rPh sb="0" eb="2">
+      <t>ヨキン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュベツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>フツウ</t>
+    </rPh>
+    <rPh sb="10" eb="12">
+      <t>トウザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>口座番号7ケタを
+半角数字で入力</t>
+    <rPh sb="0" eb="2">
+      <t>コウザ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金融機関CD
+4ケタを半角数字で入力</t>
+    <rPh sb="0" eb="2">
+      <t>キンユウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キカン</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>支店CD
+3ケタを半角数字で入力</t>
+    <rPh sb="0" eb="2">
+      <t>シテン</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>スウジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>学科・コース</t>
+    <rPh sb="0" eb="2">
+      <t>ガッカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>人数</t>
+    <rPh sb="0" eb="2">
+      <t>ニンズウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>口座名義人</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（カナ）</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>30文字までを半角カナで入力</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="9"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（氏名の間に半角でスペースを入れてください）</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>コウザ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>メイギ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ニン</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>シメイ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>アイダ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>ハンカク</t>
+    </rPh>
+    <rPh sb="39" eb="40">
+      <t>イ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">プログラム
+参加費用
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（Ａ）</t>
+    </r>
+    <rPh sb="6" eb="8">
+      <t>サンカ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>ヒヨウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>本件以外の
+支援金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（Ｂ）</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ホンケン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>イガイ</t>
+    </rPh>
+    <rPh sb="6" eb="9">
+      <t>シエンキン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">名前
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（漢字）</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カンジ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">名前
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="8"/>
+        <color theme="0"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>（カナ）</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>交付申請額</t>
+    <rPh sb="0" eb="2">
+      <t>コウフ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シンセイ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>ガク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>普通科</t>
+    <rPh sb="0" eb="3">
+      <t>フツウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>英語科</t>
+    <rPh sb="0" eb="3">
+      <t>エイゴカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>例</t>
+    <rPh sb="0" eb="1">
+      <t>レイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●●高等学校</t>
+    <rPh sb="2" eb="6">
+      <t>コウトウガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>●●科</t>
+    <rPh sb="2" eb="3">
+      <t>カ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>大阪　太郎</t>
+    <rPh sb="0" eb="2">
+      <t>オオサカ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>タロウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>オオサカ　タロウ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1111</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>111</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1111111</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｵｵｻｶ ﾀﾛｳ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>あいうえお高等学校</t>
+    <rPh sb="5" eb="9">
+      <t>コウトウガッコウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>山田　太郎</t>
+  </si>
+  <si>
+    <t>ヤマダ　タロウ</t>
+  </si>
+  <si>
+    <t>佐藤　花子</t>
+  </si>
+  <si>
+    <t>サトウ　ハナコ</t>
+  </si>
+  <si>
+    <t>鈴木　一郎</t>
+  </si>
+  <si>
+    <t>スズキ　イチロウ</t>
+  </si>
+  <si>
+    <t>高橋　美咲</t>
+  </si>
+  <si>
+    <t>タカハシ　ミサキ</t>
+  </si>
+  <si>
+    <t>田中　大輔</t>
+  </si>
+  <si>
+    <t>タナカ　ダイスケ</t>
+  </si>
+  <si>
+    <t>伊藤　由奈</t>
+  </si>
+  <si>
+    <t>イトウ　ユナ</t>
+  </si>
+  <si>
+    <t>渡辺　翔太</t>
+  </si>
+  <si>
+    <t>ワタナベ　ショウタ</t>
+  </si>
+  <si>
+    <t>中村　優衣</t>
+  </si>
+  <si>
+    <t>ナカムラ　ユイ</t>
+  </si>
+  <si>
+    <t>小林　恒一</t>
+  </si>
+  <si>
+    <t>コバヤシ　コウイチ</t>
+  </si>
+  <si>
+    <t>加藤　真理</t>
+  </si>
+  <si>
+    <t>カトウ　マリ</t>
+  </si>
+  <si>
+    <t>1234</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2234</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3234</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>4234</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>5234</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>6234</t>
+  </si>
+  <si>
+    <t>7234</t>
+  </si>
+  <si>
+    <t>8234</t>
+  </si>
+  <si>
+    <t>9234</t>
+  </si>
+  <si>
+    <t>0234</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>123</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>223</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>423</t>
+  </si>
+  <si>
+    <t>523</t>
+  </si>
+  <si>
+    <t>623</t>
+  </si>
+  <si>
+    <t>723</t>
+  </si>
+  <si>
+    <t>823</t>
+  </si>
+  <si>
+    <t>923</t>
+  </si>
+  <si>
+    <t>023</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>1234567</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>2234567</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>3234567</t>
+  </si>
+  <si>
+    <t>4234567</t>
+  </si>
+  <si>
+    <t>5234567</t>
+  </si>
+  <si>
+    <t>6234567</t>
+  </si>
+  <si>
+    <t>7234567</t>
+  </si>
+  <si>
+    <t>8234567</t>
+  </si>
+  <si>
+    <t>9234567</t>
+  </si>
+  <si>
+    <t>10234567</t>
+  </si>
+  <si>
+    <t>ﾔﾏﾀﾞﾀﾛｳ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｻﾄｳ ﾊﾅｺ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｽｽﾞｷ ｲﾁﾛｳ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ﾀｶﾊｼ ﾐｻｷ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ﾀﾅｶ ﾀﾞｲｽｹ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｲﾄｳ ﾕﾅ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ﾅｶﾑﾗ ﾕｲ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｶﾄｳ ﾏﾘ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ｺﾊﾞﾔｼ ｼﾖｳｲﾁ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ﾜﾀﾅﾍﾞ ｼﾖｳﾀ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="#,##0&quot;円&quot;"/>
+  </numFmts>
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <name val="Calibri"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
       <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="0"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="0"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <scheme val="minor"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Meiryo UI"/>
+      <family val="2"/>
+      <charset val="128"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="4">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -42,92 +750,513 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="hair">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dashed">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </left>
+      <right style="medium">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </right>
+      <top style="dotted">
+        <color theme="0" tint="-0.34998626667073579"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="47">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="3" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="2">
+    <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -165,7 +1294,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -199,6 +1328,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -233,9 +1363,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -408,66 +1539,1057 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A4662CE-BCEB-443D-B625-A7DCD60FD011}">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:N24"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="15.77734375" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.109375" customWidth="1"/>
+    <col min="9" max="9" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16" style="8" customWidth="1"/>
+    <col min="11" max="11" width="16.109375" style="8" customWidth="1"/>
+    <col min="12" max="12" width="7.44140625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="13" style="8" customWidth="1"/>
+    <col min="14" max="14" width="31.44140625" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>学校名</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>名前（漢字）</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>交付申請額</t>
-        </is>
+    <row r="1" spans="1:14" s="1" customFormat="1" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="L1" s="21" t="s">
+        <v>2</v>
+      </c>
+      <c r="M1" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="N1" s="22" t="s">
+        <v>8</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>例●●高等学校</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>大阪　太郎</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
+    <row r="2" spans="1:14" s="15" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="41">
+        <v>2</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="42" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" s="43">
+        <v>300000</v>
+      </c>
+      <c r="H2" s="43">
+        <v>0</v>
+      </c>
+      <c r="I2" s="43">
+        <f>ROUNDDOWN(IF(G2-H2&gt;=100000,100000,IF(G2-H2&lt;100000,G2-H2)),-3)</f>
+        <v>100000</v>
+      </c>
+      <c r="J2" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="45" t="s">
+        <v>25</v>
+      </c>
+      <c r="L2" s="45" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="45" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="46" t="s">
+        <v>27</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>あいうえお高等学校</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>山田　太郎</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>100000</t>
-        </is>
-      </c>
+    <row r="3" spans="1:14" s="15" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="9">
+        <v>2</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10">
+        <f t="shared" ref="I3:I22" si="0">ROUNDDOWN(IF(G3-H3&gt;=100000,100000,IF(G3-H3&lt;100000,G3-H3)),-3)</f>
+        <v>100000</v>
+      </c>
+      <c r="J3" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="K3" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="M3" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="N3" s="25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>2</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="9">
+        <v>2</v>
+      </c>
+      <c r="E4" s="14" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0</v>
+      </c>
+      <c r="I4" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J4" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="K4" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="L4" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="N4" s="28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="9">
+        <v>2</v>
+      </c>
+      <c r="E5" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="G5" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0</v>
+      </c>
+      <c r="I5" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="K5" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="27" t="s">
+        <v>18</v>
+      </c>
+      <c r="M5" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="N5" s="28" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>4</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="9">
+        <v>2</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>52</v>
+      </c>
+      <c r="K6" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="L6" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="N6" s="28" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="9">
+        <v>2</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0</v>
+      </c>
+      <c r="I7" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J7" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="K7" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="28" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>6</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="9">
+        <v>2</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0</v>
+      </c>
+      <c r="I8" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J8" s="23" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="N8" s="28" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" s="9">
+        <v>2</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0</v>
+      </c>
+      <c r="I9" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J9" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M9" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>8</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="9">
+        <v>2</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="G10" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0</v>
+      </c>
+      <c r="I10" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J10" s="26" t="s">
+        <v>56</v>
+      </c>
+      <c r="K10" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="N10" s="28" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="9">
+        <v>2</v>
+      </c>
+      <c r="E11" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0</v>
+      </c>
+      <c r="I11" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J11" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="N11" s="28" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="11">
+        <v>10</v>
+      </c>
+      <c r="B12" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="9">
+        <v>2</v>
+      </c>
+      <c r="E12" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="G12" s="10">
+        <v>459000</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0</v>
+      </c>
+      <c r="I12" s="10">
+        <f t="shared" si="0"/>
+        <v>100000</v>
+      </c>
+      <c r="J12" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="L12" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="N12" s="28" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="11"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="9"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="26"/>
+      <c r="K13" s="27"/>
+      <c r="L13" s="27"/>
+      <c r="M13" s="27"/>
+      <c r="N13" s="28"/>
+    </row>
+    <row r="14" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="11"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="9"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+      <c r="G14" s="10"/>
+      <c r="H14" s="10"/>
+      <c r="I14" s="10"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="27"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="28"/>
+    </row>
+    <row r="15" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="11"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="10"/>
+      <c r="H15" s="10"/>
+      <c r="I15" s="10"/>
+      <c r="J15" s="26"/>
+      <c r="K15" s="27"/>
+      <c r="L15" s="27"/>
+      <c r="M15" s="27"/>
+      <c r="N15" s="28"/>
+    </row>
+    <row r="16" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="32"/>
+      <c r="B16" s="13"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="10"/>
+      <c r="H16" s="10"/>
+      <c r="I16" s="34"/>
+      <c r="J16" s="35"/>
+      <c r="K16" s="36"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="37"/>
+    </row>
+    <row r="17" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="32"/>
+      <c r="B17" s="13"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="36"/>
+      <c r="L17" s="36"/>
+      <c r="M17" s="36"/>
+      <c r="N17" s="37"/>
+    </row>
+    <row r="18" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="32"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="36"/>
+      <c r="L18" s="36"/>
+      <c r="M18" s="36"/>
+      <c r="N18" s="37"/>
+    </row>
+    <row r="19" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="32"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="36"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="37"/>
+    </row>
+    <row r="20" spans="1:14" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="32"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="33"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="36"/>
+      <c r="L20" s="36"/>
+      <c r="M20" s="36"/>
+      <c r="N20" s="37"/>
+    </row>
+    <row r="21" spans="1:14" s="12" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="32"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="37"/>
+    </row>
+    <row r="22" spans="1:14" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="16"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="17"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="18"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="30"/>
+      <c r="L22" s="30"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="31"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A23" s="15"/>
+      <c r="G23" s="7"/>
+      <c r="H23" s="7"/>
+      <c r="I23" s="7"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="C24" s="38"/>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <autoFilter ref="A1:N22" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="1"/>
+  <dataValidations count="5">
+    <dataValidation type="textLength" imeMode="fullKatakana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N53:N1048576" xr:uid="{88345F3E-73BD-4FDE-91A9-8740B9BCCB12}">
+      <formula1>0</formula1>
+      <formula2>30</formula2>
+    </dataValidation>
+    <dataValidation imeMode="halfAlpha" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J53:M1048576 D2:D22 G2:G22 J1:M22" xr:uid="{3F057349-FD0E-46FD-BC59-BFF9FDD61089}"/>
+    <dataValidation imeMode="fullKatakana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F22 N1" xr:uid="{200A6265-8E0C-4052-B26E-5D1995522E28}"/>
+    <dataValidation imeMode="hiragana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E22" xr:uid="{17E778BB-C573-4FA8-A569-526BC54C54B2}"/>
+    <dataValidation type="textLength" imeMode="halfKatakana" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N2:N22" xr:uid="{955D20A3-E3FF-4058-9DC2-AC88E1C997F5}">
+      <formula1>0</formula1>
+      <formula2>30</formula2>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.70866141732283472" right="0.42" top="0.74803149606299213" bottom="0.55000000000000004" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="54" orientation="landscape" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;L&amp;"Meiryo UI,太字"&amp;20&amp;A</oddHeader>
+  </headerFooter>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="ドキュメント" ma:contentTypeID="0x010100EF74CF8F5D8DFE40BFEBBC0515F65BBA" ma:contentTypeVersion="15" ma:contentTypeDescription="新しいドキュメントを作成します。" ma:contentTypeScope="" ma:versionID="8a888e1d3bb353cec0ecb9d333a331a4">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6550dd01-367c-449d-bd6c-c9c4cc785824" xmlns:ns3="92c85782-91b6-4975-a634-e8e07eaefb77" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a2adcb97fe0a807aac4180f84ea8f242" ns2:_="" ns3:_="">
+    <xsd:import namespace="6550dd01-367c-449d-bd6c-c9c4cc785824"/>
+    <xsd:import namespace="92c85782-91b6-4975-a634-e8e07eaefb77"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:RetentionLimitDate" minOccurs="0"/>
+                <xsd:element ref="ns2:RetentionPeriodDate" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceBillingMetadata" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6550dd01-367c-449d-bd6c-c9c4cc785824" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="RetentionLimitDate" ma:index="11" nillable="true" ma:displayName="保存年限" ma:format="DateOnly" ma:internalName="RetentionLimitDate">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="RetentionPeriodDate" ma:index="12" nillable="true" ma:displayName="保存期間" ma:default="" ma:format="Dropdown" ma:internalName="RetentionPeriodDate">
+      <xsd:simpleType>
+        <xsd:union memberTypes="dms:Text">
+          <xsd:simpleType>
+            <xsd:restriction base="dms:Choice">
+              <xsd:enumeration value="1年間"/>
+              <xsd:enumeration value="3年間"/>
+              <xsd:enumeration value="5年間"/>
+              <xsd:enumeration value="10年間"/>
+              <xsd:enumeration value="20年間"/>
+              <xsd:enumeration value="長期"/>
+            </xsd:restriction>
+          </xsd:simpleType>
+        </xsd:union>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="13" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="16" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="19" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="画像タグ" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="5efb9172-ed01-4b15-a485-c06beb5524f5" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="21" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceBillingMetadata" ma:index="22" nillable="true" ma:displayName="MediaServiceBillingMetadata" ma:hidden="true" ma:internalName="MediaServiceBillingMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="92c85782-91b6-4975-a634-e8e07eaefb77" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="TaxCatchAll" ma:index="20" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{16bc986b-5023-4cd4-99bd-2fe173f2cf6d}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="92c85782-91b6-4975-a634-e8e07eaefb77">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="コンテンツ タイプ"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="タイトル"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <RetentionLimitDate xmlns="6550dd01-367c-449d-bd6c-c9c4cc785824" xsi:nil="true"/>
+    <RetentionPeriodDate xmlns="6550dd01-367c-449d-bd6c-c9c4cc785824" xsi:nil="true"/>
+    <TaxCatchAll xmlns="92c85782-91b6-4975-a634-e8e07eaefb77" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="6550dd01-367c-449d-bd6c-c9c4cc785824">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65F6E9E7-E0D4-4333-BAC8-CABFC99D766E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{38376912-46F6-4175-A3F6-0314D3F4E87E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="6550dd01-367c-449d-bd6c-c9c4cc785824"/>
+    <ds:schemaRef ds:uri="92c85782-91b6-4975-a634-e8e07eaefb77"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9E90AE8E-867D-49E4-852E-5ED9730FE8FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="92c85782-91b6-4975-a634-e8e07eaefb77"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="6550dd01-367c-449d-bd6c-c9c4cc785824"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{c5ee6e94-d455-43df-b19e-97dde671e91e}" enabled="1" method="Standard" siteId="{12070d49-0d58-40e3-8d87-8f8077d1ef42}" removed="0"/>
+</clbl:labelList>
 </file>